--- a/assets/101-GR-01 GRIT REMOVAL PACKAGE.xlsx
+++ b/assets/101-GR-01 GRIT REMOVAL PACKAGE.xlsx
@@ -848,7 +848,7 @@
       <c r="H11" s="11" t="n"/>
       <c r="I11" s="12" t="inlineStr">
         <is>
-          <t>m³/h</t>
+          <t>m³/d</t>
         </is>
       </c>
       <c r="J11" s="13" t="n"/>
